--- a/data/output/evaluasi_91.xlsx
+++ b/data/output/evaluasi_91.xlsx
@@ -8,7 +8,13 @@
   </bookViews>
   <sheets>
     <sheet name="9100" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="9101" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="9102" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="9101" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="9103" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="9104" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="9105" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="9111" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="9112" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -426,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:F50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -472,20 +478,20 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>5.240453038125557</v>
+        <v>6.261994810413276</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>adhb_pi_q1-25</t>
+          <t>adhb_pi_q3-25</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Diskrepansi lebih dari +- 5 persen</t>
+          <t>Diskrepansi ADHB antara Provinsi dan total Kabupaten/Kota lebih dari (+-5%)</t>
         </is>
       </c>
     </row>
@@ -504,7 +510,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>5.058082659251527</v>
+        <v>13.35032167588513</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -513,7 +519,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Diskrepansi lebih dari +- 5 persen</t>
+          <t>Diskrepansi ADHK antara Provinsi dan total Kabupaten/Kota lebih dari (+-5%)</t>
         </is>
       </c>
     </row>
@@ -532,7 +538,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>-0.5096642428429614</v>
+        <v>-0.6970559329108278</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -541,7 +547,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Growth berlawanan arah</t>
+          <t>Nilai antara Provinsi dan total Kabupaten/Kota beda arah</t>
         </is>
       </c>
     </row>
@@ -556,20 +562,20 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>q2-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1.702989373818466</v>
+        <v>1.178902031398771</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>q-to-q_pklnprt_q2-25 vs q-to-q_pklnprt_q2-25.1</t>
+          <t>q-to-q_pdrb_q3-25 vs q-to-q_pdrb_q3-25.1</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Growth lebih dari +- 2 kalinya</t>
+          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,3 point)</t>
         </is>
       </c>
     </row>
@@ -584,20 +590,20 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>q2-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>-0.8785946179563303</v>
+        <v>-0.3476154453474248</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>implisit_q-to-q_pdrb_q2-25 vs implisit_q-to-q_pdrb_q2-25.1</t>
+          <t>q-to-q_pklnprt_q3-25 vs q-to-q_pklnprt_q3-25.1</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Growth lebih dari +- 2 kalinya</t>
+          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
         </is>
       </c>
     </row>
@@ -616,16 +622,16 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>1.957454670845629</v>
+        <v>6.820563932745524</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>implisit_q-to-q_pklnprt_q2-25 vs implisit_q-to-q_pklnprt_q2-25.1</t>
+          <t>q-to-q_pkp_q2-25 vs q-to-q_pkp_q2-25.1</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Growth lebih dari +- 2 kalinya</t>
+          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
         </is>
       </c>
     </row>
@@ -640,20 +646,20 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>q2-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>2.445932331783739</v>
+        <v>12.00804723417216</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>implisit_q-to-q_pkp_q2-25 vs implisit_q-to-q_pkp_q2-25.1</t>
+          <t>q-to-q_pkp_q3-25 vs q-to-q_pkp_q3-25.1</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Growth lebih dari +- 2 kalinya</t>
+          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
         </is>
       </c>
     </row>
@@ -668,20 +674,20 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q2-25</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>2.135835006211487</v>
+        <v>3.533461036330812</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>implisit_y-on-y_pkrt_q1-25 vs implisit_y-on-y_pkrt_q1-25.1</t>
+          <t>q-to-q_pmtb_q2-25 vs q-to-q_pmtb_q2-25.1</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Growth lebih dari +- 2 kalinya</t>
+          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
         </is>
       </c>
     </row>
@@ -696,20 +702,1140 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>7.300908986261256</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>q-to-q_pmtb_q3-25 vs q-to-q_pmtb_q3-25.1</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>91</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Papua Barat</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>-0.05396075755322658</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>y-on-y_pdrb_q3-25 vs y-on-y_pdrb_q3-25.1</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,01 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>91</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Papua Barat</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>3.741963806958744</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>y-on-y_pkrt_q1-25 vs y-on-y_pkrt_q1-25.1</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>91</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Papua Barat</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
           <t>q2-25</t>
         </is>
       </c>
-      <c r="D10" t="n">
-        <v>2.422156358714426</v>
-      </c>
-      <c r="E10" t="inlineStr">
+      <c r="D13" t="n">
+        <v>2.1863161306231</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>y-on-y_pkrt_q2-25 vs y-on-y_pkrt_q2-25.1</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>91</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Papua Barat</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>2.984272264914886</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>y-on-y_pkrt_q3-25 vs y-on-y_pkrt_q3-25.1</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,05 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>91</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Papua Barat</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>7.522446153328223</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q2-25 vs y-on-y_pklnprt_q2-25.1</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>91</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Papua Barat</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>11.57942139508593</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q3-25 vs y-on-y_pklnprt_q3-25.1</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,05 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>91</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Papua Barat</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>5.453394434712981</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q1-25 vs y-on-y_pkp_q1-25.1</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>91</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Papua Barat</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>6.605969160628344</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q2-25 vs y-on-y_pkp_q2-25.1</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>91</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Papua Barat</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>-1.090574217516447</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q3-25 vs y-on-y_pkp_q3-25.1</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Nilai antara Provinsi dan total Kabupaten/Kota beda arah</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>91</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Papua Barat</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>-4.481764789927438</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q2-25 vs y-on-y_pmtb_q2-25.1</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>91</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Papua Barat</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>-3.631327714630073</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q3-25 vs y-on-y_pmtb_q3-25.1</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,05 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>91</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Papua Barat</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>3.741963806958744</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>c-to-c_pkrt_q1-25 vs c-to-c_pkrt_q1-25.1</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>91</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Papua Barat</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>2.954658022781779</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>c-to-c_pkrt_q2-25 vs c-to-c_pkrt_q2-25.1</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>91</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Papua Barat</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>2.964563673700061</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>c-to-c_pkrt_q3-25 vs c-to-c_pkrt_q3-25.1</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>91</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Papua Barat</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>6.175227363625707</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>c-to-c_pklnprt_q3-25 vs c-to-c_pklnprt_q3-25.1</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>91</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Papua Barat</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>5.453394434712981</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q1-25 vs c-to-c_pkp_q1-25.1</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>91</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Papua Barat</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>6.045557337439343</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q2-25 vs c-to-c_pkp_q2-25.1</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>91</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Papua Barat</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>3.313771791999619</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q3-25 vs c-to-c_pkp_q3-25.1</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>91</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Papua Barat</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>-3.489528254123059</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>c-to-c_pmtb_q2-25 vs c-to-c_pmtb_q2-25.1</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>91</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Papua Barat</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>-3.539644364175615</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>c-to-c_pmtb_q3-25 vs c-to-c_pmtb_q3-25.1</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>91</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Papua Barat</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>1.182965277088706</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pdrb_q1-25 vs implisit_q-to-q_pdrb_q1-25.1</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Diskrepansi Implisit Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>91</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Papua Barat</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>-0.5255008862323157</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pdrb_q3-25 vs implisit_q-to-q_pdrb_q3-25.1</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Nilai antara Provinsi dan total Kabupaten/Kota beda arah</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>91</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Papua Barat</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>1.263932766184529</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkrt_q1-25 vs implisit_q-to-q_pkrt_q1-25.1</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Diskrepansi Implisit Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>91</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Papua Barat</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>1.38550028944673</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkrt_q2-25 vs implisit_q-to-q_pkrt_q2-25.1</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Diskrepansi Implisit Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>91</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Papua Barat</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>-2.186976546749063</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pklnprt_q1-25 vs implisit_q-to-q_pklnprt_q1-25.1</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Diskrepansi Implisit Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>91</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Papua Barat</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>1.508600130303066</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pklnprt_q3-25 vs implisit_q-to-q_pklnprt_q3-25.1</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Diskrepansi Implisit Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>91</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Papua Barat</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>-4.583825674035403</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkp_q1-25 vs implisit_q-to-q_pkp_q1-25.1</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Diskrepansi Implisit Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>91</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Papua Barat</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>2.410945011042196</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkp_q2-25 vs implisit_q-to-q_pkp_q2-25.1</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Diskrepansi Implisit Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>91</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Papua Barat</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>3.491996062969358</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pmtb_q3-25 vs implisit_q-to-q_pmtb_q3-25.1</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Diskrepansi Implisit Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>91</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Papua Barat</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>2.397035228534372</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pdrb_q1-25 vs implisit_y-on-y_pdrb_q1-25.1</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Diskrepansi Implisit Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>91</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Papua Barat</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>2.165082566770136</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pkrt_q1-25 vs implisit_y-on-y_pkrt_q1-25.1</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Diskrepansi Implisit Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>91</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Papua Barat</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>2.447951023530619</v>
+      </c>
+      <c r="E42" t="inlineStr">
         <is>
           <t>implisit_y-on-y_pkrt_q2-25 vs implisit_y-on-y_pkrt_q2-25.1</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Growth lebih dari +- 2 kalinya</t>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Diskrepansi Implisit Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>91</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Papua Barat</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>-5.37407514992239</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pklnprt_q1-25 vs implisit_y-on-y_pklnprt_q1-25.1</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Diskrepansi Implisit Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>91</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Papua Barat</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>-1.615397615789796</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pklnprt_q2-25 vs implisit_y-on-y_pklnprt_q2-25.1</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Diskrepansi Implisit Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>91</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Papua Barat</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>0.527618837560937</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pklnprt_q3-25 vs implisit_y-on-y_pklnprt_q3-25.1</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Diskrepansi Implisit Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>91</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Papua Barat</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>4.95513818951722</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pkp_q1-25 vs implisit_y-on-y_pkp_q1-25.1</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Diskrepansi Implisit Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>91</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Papua Barat</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>1.706934078865211</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pkp_q2-25 vs implisit_y-on-y_pkp_q2-25.1</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Diskrepansi Implisit Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>91</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Papua Barat</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>2.646136573794842</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pkp_q3-25 vs implisit_y-on-y_pkp_q3-25.1</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Diskrepansi Implisit Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>91</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Papua Barat</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>2.348154022918763</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pmtb_q2-25 vs implisit_y-on-y_pmtb_q2-25.1</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Diskrepansi Implisit Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>91</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Papua Barat</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>-0.01494832000629318</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pmtb_q3-25 vs implisit_y-on-y_pmtb_q3-25.1</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Nilai antara Provinsi dan total Kabupaten/Kota beda arah</t>
         </is>
       </c>
     </row>
@@ -724,7 +1850,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -761,6 +1887,1004 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
+        <v>9102</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kabupaten Kaimana</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>-11088.36404301494</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>adhb_net_ekspor_q1-25_ril vs adhb_net_ekspor_q1-25_rev</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Nilai revisi lebih dari (+-30%) dari nilai rilis</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>9102</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Kaimana</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>-61834.41067619598</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>adhb_net_ekspor_q2-25_ril vs adhb_net_ekspor_q2-25_rev</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Nilai revisi lebih dari (+-30%) dari nilai rilis</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>9102</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Kaimana</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>-26550.70015604619</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>adhk_pi_q1-25_ril vs adhk_pi_q1-25_rev</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Nilai revisi lebih dari (+-30%) dari nilai rilis</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>9102</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Kaimana</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>-41969.1491067171</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>adhk_pi_q2-25_ril vs adhk_pi_q2-25_rev</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Nilai revisi lebih dari (+-30%) dari nilai rilis</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>9102</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Kaimana</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>41.02817315754022</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>distribusi_pkp_q1-25_ril vs distribusi_pkp_q1-25_rev</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Nilai revisi lebih dari (+-5 point) dari nilai rilis</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>9102</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Kaimana</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>-1.474611516071291</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>distribusi_net_ekspor_q1-25_ril vs distribusi_net_ekspor_q1-25_rev</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Nilai revisi lebih dari (+-5 point) dari nilai rilis</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>9102</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kabupaten Kaimana</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>-23.58426491050116</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q1-25_ril vs q-to-q_pkp_q1-25_rev</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Nilai revisi lebih dari (+-4 point) dari nilai rilis</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>9102</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kabupaten Kaimana</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>17.41085063626756</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q2-25_ril vs q-to-q_pkp_q2-25_rev</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Nilai revisi lebih dari (+-4 point) dari nilai rilis</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9102</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kabupaten Kaimana</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>-29.65943211644677</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>q-to-q_pmtb_q1-25_ril vs q-to-q_pmtb_q1-25_rev</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Nilai revisi lebih dari (+-4 point) dari nilai rilis</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>9102</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Kabupaten Kaimana</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>0.4366332710283526</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q1-25_ril vs y-on-y_pkp_q1-25_rev</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Nilai revisi lebih dari (+-4 point) dari nilai rilis</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>9102</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Kabupaten Kaimana</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>16.19628368666374</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q2-25_ril vs y-on-y_pkp_q2-25_rev</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Nilai revisi lebih dari (+-4 point) dari nilai rilis</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>9102</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Kabupaten Kaimana</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>1.090521569303796</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q1-25_ril vs y-on-y_pmtb_q1-25_rev</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Nilai revisi lebih dari (+-4 point) dari nilai rilis</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>9102</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Kabupaten Kaimana</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>3.753446142042751</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q2-25_ril vs y-on-y_pmtb_q2-25_rev</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Nilai revisi lebih dari (+-4 point) dari nilai rilis</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>9102</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Kabupaten Kaimana</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>0.4366332710283526</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q1-25_ril vs c-to-c_pkp_q1-25_rev</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Nilai revisi lebih dari (+-4 point) dari nilai rilis</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>9102</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Kabupaten Kaimana</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>8.374591991727174</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q2-25_ril vs c-to-c_pkp_q2-25_rev</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Nilai revisi lebih dari (+-4 point) dari nilai rilis</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>9102</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Kabupaten Kaimana</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>1.090521569303796</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>c-to-c_pmtb_q1-25_ril vs c-to-c_pmtb_q1-25_rev</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Nilai revisi lebih dari (+-4 point) dari nilai rilis</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>9102</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Kabupaten Kaimana</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>2.469464323116962</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>c-to-c_pmtb_q2-25_ril vs c-to-c_pmtb_q2-25_rev</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Nilai revisi lebih dari (+-4 point) dari nilai rilis</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>9102</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Kabupaten Kaimana</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>14.26605872396661</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>sog_q_pi_q1-25_ril vs sog_q_pi_q1-25_rev</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>9102</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Kabupaten Kaimana</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>-3.535964832523272</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>sog_q_pi_q2-25_ril vs sog_q_pi_q2-25_rev</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>9102</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Kabupaten Kaimana</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>-11.01182592378829</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>sog_y-on-y_pi_q1-25_ril vs sog_y-on-y_pi_q1-25_rev</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>9102</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Kabupaten Kaimana</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>-5.678571844405251</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>sog_y-on-y_pi_q2-25_ril vs sog_y-on-y_pi_q2-25_rev</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>9102</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Kabupaten Kaimana</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>4.599254592745324</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>q-to-q_pdrb_q3-25_prov vs q-to-q_pdrb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>9102</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Kabupaten Kaimana</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>-1.459975158230145</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>q-to-q_pkrt_q3-25_prov vs q-to-q_pkrt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>9102</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Kabupaten Kaimana</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>0.2548528358984035</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q3-25_prov vs q-to-q_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>9102</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Kabupaten Kaimana</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>10.12298266182615</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>q-to-q_pmtb_q3-25_prov vs q-to-q_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>9102</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Kabupaten Kaimana</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>3.551711271843557</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>y-on-y_pdrb_q3-25_prov vs y-on-y_pdrb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>9102</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Kabupaten Kaimana</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>25.21698047990715</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q3-25_prov vs y-on-y_pklnprt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>9102</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Kabupaten Kaimana</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>-4.044567417975975</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q3-25_prov vs y-on-y_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>9102</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Kabupaten Kaimana</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>0.2390813300992643</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>c-to-c_pdrb_q3-25_prov vs c-to-c_pdrb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>9102</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Kabupaten Kaimana</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>1.361809348920523</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>c-to-c_pkrt_q3-25_prov vs c-to-c_pkrt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>9102</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Kabupaten Kaimana</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>-1.640937718119766</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pklnprt_q3-25_prov vs implisit_y-on-y_pklnprt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>9102</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Kabupaten Kaimana</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>1.191810877780068</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pkp_q3-25_prov vs implisit_y-on-y_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>9102</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Kabupaten Kaimana</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>9.93892982689405</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pmtb_q3-25_prov vs implisit_y-on-y_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>9102</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Kabupaten Kaimana</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>6.318798430862557</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>sog_q_pi_q3-25</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
         <v>9101</v>
       </c>
       <c r="B2" t="inlineStr">
@@ -770,20 +2894,20 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q2-25</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>-3.381095951391177</v>
+        <v>0.0007200057679199482</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>implisit_q-to-q_pklnprt_q1-25_ril vs implisit_q-to-q_pklnprt_q1-25_rev</t>
+          <t>implisit_y-on-y_pdrb_q2-25_ril vs implisit_y-on-y_pdrb_q2-25_rev</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Growth revisi berlawanan arah</t>
+          <t>Nilai revisi dan nilai rilis beda arah</t>
         </is>
       </c>
     </row>
@@ -802,16 +2926,2682 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>-3.43686101233614</v>
+        <v>-2.970345749557216</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>implisit_y-on-y_pklnprt_q1-25_ril vs implisit_y-on-y_pklnprt_q1-25_rev</t>
+          <t>sog_q_pi_q1-25_ril vs sog_q_pi_q1-25_rev</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Growth revisi berlawanan arah</t>
+          <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>9101</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Fakfak</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>-3.899207837827265</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>sog_q_pi_q2-25_ril vs sog_q_pi_q2-25_rev</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>9101</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Fakfak</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>-2.212557580026331</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>sog_y-on-y_pi_q1-25_ril vs sog_y-on-y_pi_q1-25_rev</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>9101</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Fakfak</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>-0.8722893328536987</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>q-to-q_pkrt_q3-25_prov vs q-to-q_pkrt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>9101</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Fakfak</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>3.706947216451338</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>y-on-y_pdrb_q3-25_prov vs y-on-y_pdrb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>9101</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kabupaten Fakfak</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>13.79620526962119</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q3-25_prov vs y-on-y_pklnprt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>9101</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kabupaten Fakfak</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>-1.104970475116965</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q3-25_prov vs y-on-y_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9101</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kabupaten Fakfak</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>2.566291005960116</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q3-25_prov vs y-on-y_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>9101</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Kabupaten Fakfak</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>1.892137387935406</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>c-to-c_pdrb_q3-25_prov vs c-to-c_pdrb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>9101</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Kabupaten Fakfak</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>-0.2692694566067505</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q3-25_prov vs c-to-c_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>9101</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Kabupaten Fakfak</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>3.38192122480197</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>c-to-c_pmtb_q3-25_prov vs c-to-c_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>9101</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Kabupaten Fakfak</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>-0.5916609473926189</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pdrb_q3-25_prov vs implisit_q-to-q_pdrb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>9101</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Kabupaten Fakfak</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>3.05574449382478</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pmtb_q3-25_prov vs implisit_q-to-q_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>9101</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Kabupaten Fakfak</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>0.5311781024651786</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pkp_q3-25_prov vs implisit_y-on-y_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>9101</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Kabupaten Fakfak</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>-2.476232960412742</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pmtb_q3-25_prov vs implisit_y-on-y_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>9101</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Kabupaten Fakfak</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>-4.690003585299495</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>sog_q_pi_q3-25</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>9101</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Kabupaten Fakfak</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>2.471256170685916</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>sog_y-on-y_pi_q3-25</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>9103</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kabupaten Teluk Wondama</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>4.381082976428453</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>sog_q_pi_q1-25_ril vs sog_q_pi_q1-25_rev</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>9103</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Teluk Wondama</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>-5.458536884744589</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>sog_q_pi_q2-25_ril vs sog_q_pi_q2-25_rev</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>9103</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Teluk Wondama</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>-5.12180441991236</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>sog_y-on-y_pi_q1-25_ril vs sog_y-on-y_pi_q1-25_rev</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>9103</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Teluk Wondama</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>-10.26134321665002</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>sog_y-on-y_pi_q2-25_ril vs sog_y-on-y_pi_q2-25_rev</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>9103</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Teluk Wondama</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>2.444726657498813</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>q-to-q_pklnprt_q3-25_prov vs q-to-q_pklnprt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>9103</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Teluk Wondama</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>13.78319463654736</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>q-to-q_pmtb_q3-25_prov vs q-to-q_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>9103</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kabupaten Teluk Wondama</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>1.473337298860992</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>y-on-y_pdrb_q3-25_prov vs y-on-y_pdrb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>9103</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kabupaten Teluk Wondama</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>12.3892032894632</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q3-25_prov vs y-on-y_pklnprt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9103</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kabupaten Teluk Wondama</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>-5.002909999999996</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q3-25_prov vs y-on-y_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>9103</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Kabupaten Teluk Wondama</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>6.35631605149406</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q3-25_prov vs y-on-y_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>9103</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Kabupaten Teluk Wondama</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>0.9313696395480053</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>c-to-c_pdrb_q3-25_prov vs c-to-c_pdrb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>9103</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Kabupaten Teluk Wondama</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>8.746768789298761</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>c-to-c_pklnprt_q3-25_prov vs c-to-c_pklnprt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>9103</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Kabupaten Teluk Wondama</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>0.05913215877384081</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q3-25_prov vs c-to-c_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>9103</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Kabupaten Teluk Wondama</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>0.9326950003596324</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>c-to-c_pmtb_q3-25_prov vs c-to-c_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>9103</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Kabupaten Teluk Wondama</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>-1.764493503699347</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pdrb_q3-25_prov vs implisit_q-to-q_pdrb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>9103</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Kabupaten Teluk Wondama</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>3.900829385180268</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pmtb_q3-25_prov vs implisit_q-to-q_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>9103</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Kabupaten Teluk Wondama</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>1.293295271718237</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pkp_q3-25_prov vs implisit_y-on-y_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>9103</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Kabupaten Teluk Wondama</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>5.059910708569663</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>sog_q_pi_q3-25</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>9104</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kabupaten Teluk Bintuni</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>-5.445974570095401</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>sog_q_pi_q1-25_ril vs sog_q_pi_q1-25_rev</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>9104</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Teluk Bintuni</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>4.803032957012347</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>sog_q_pi_q2-25_ril vs sog_q_pi_q2-25_rev</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>9104</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Teluk Bintuni</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>-13.25011205589186</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>sog_y-on-y_pi_q1-25_ril vs sog_y-on-y_pi_q1-25_rev</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>9104</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Teluk Bintuni</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>-10.90478199695595</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>sog_y-on-y_pi_q2-25_ril vs sog_y-on-y_pi_q2-25_rev</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>9104</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Teluk Bintuni</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>0.7346442042813418</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>q-to-q_pklnprt_q3-25_prov vs q-to-q_pklnprt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>9104</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Teluk Bintuni</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>-6.210015512065828</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q3-25_prov vs y-on-y_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>9104</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kabupaten Teluk Bintuni</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>-10.26473775497234</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q3-25_prov vs y-on-y_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>9104</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kabupaten Teluk Bintuni</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>-10.52630280730819</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>c-to-c_pmtb_q3-25_prov vs c-to-c_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9104</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kabupaten Teluk Bintuni</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>-0.6604798485046666</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pdrb_q3-25_prov vs implisit_q-to-q_pdrb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>9104</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Kabupaten Teluk Bintuni</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>4.444418963099687</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pmtb_q3-25_prov vs implisit_q-to-q_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>9104</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Kabupaten Teluk Bintuni</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>3.077969534198349</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>sog_q_pi_q3-25</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>9105</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kabupaten Manokwari</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>14.13919446469299</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>sog_q_pi_q1-25_ril vs sog_q_pi_q1-25_rev</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>9105</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Manokwari</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>22.43752220427837</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>sog_q_pi_q2-25_ril vs sog_q_pi_q2-25_rev</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>9105</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Manokwari</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>-5.805106813552792</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>sog_y-on-y_pi_q1-25_ril vs sog_y-on-y_pi_q1-25_rev</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>9105</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Manokwari</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>32.04772144777929</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>sog_y-on-y_pi_q2-25_ril vs sog_y-on-y_pi_q2-25_rev</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>9105</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Manokwari</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>3.690836871825701</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>y-on-y_pdrb_q3-25_prov vs y-on-y_pdrb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>9105</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Manokwari</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>10.76368497996713</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q3-25_prov vs y-on-y_pklnprt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>9105</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kabupaten Manokwari</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>4.213916855572595</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q3-25_prov vs y-on-y_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>9105</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kabupaten Manokwari</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>-0.1792885430719491</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pdrb_q3-25_prov vs implisit_q-to-q_pdrb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9105</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kabupaten Manokwari</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>1.865423835480416</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pmtb_q3-25_prov vs implisit_q-to-q_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>9105</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Kabupaten Manokwari</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>-3.350220787922625</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pklnprt_q3-25_prov vs implisit_y-on-y_pklnprt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>9105</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Kabupaten Manokwari</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>0.641575160264077</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pkp_q3-25_prov vs implisit_y-on-y_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>9105</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Kabupaten Manokwari</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>-2.165844482731761</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pmtb_q3-25_prov vs implisit_y-on-y_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>9105</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Kabupaten Manokwari</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>-28.29874969245179</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>sog_q_pi_q3-25</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>9105</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Kabupaten Manokwari</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>-3.040292795680795</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>sog_y-on-y_pi_q3-25</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>9111</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kabupaten Manokwari Selatan</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>8.526994283983605</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>sog_q_pi_q1-25_ril vs sog_q_pi_q1-25_rev</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>9111</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Manokwari Selatan</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>-4.610760508915605</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>sog_q_pi_q2-25_ril vs sog_q_pi_q2-25_rev</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>9111</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Manokwari Selatan</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>-8.404412331027061</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>sog_y-on-y_pi_q1-25_ril vs sog_y-on-y_pi_q1-25_rev</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>9111</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Manokwari Selatan</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>-9.888803123716807</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>sog_y-on-y_pi_q2-25_ril vs sog_y-on-y_pi_q2-25_rev</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>9111</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Manokwari Selatan</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>0.2142999999999368</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>q-to-q_pklnprt_q3-25_prov vs q-to-q_pklnprt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>9111</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Manokwari Selatan</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>1.424000000000075</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q3-25_prov vs q-to-q_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>9111</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kabupaten Manokwari Selatan</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>1.153444034324987</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>q-to-q_pmtb_q3-25_prov vs q-to-q_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>9111</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kabupaten Manokwari Selatan</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>1.308039812949664</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>y-on-y_pdrb_q3-25_prov vs y-on-y_pdrb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9111</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kabupaten Manokwari Selatan</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>2.038264440216733</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q3-25_prov vs y-on-y_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>9111</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Kabupaten Manokwari Selatan</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>0.8143057087105819</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>c-to-c_pmtb_q3-25_prov vs c-to-c_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>9111</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Kabupaten Manokwari Selatan</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>-1.641061313712278</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pdrb_q3-25_prov vs implisit_q-to-q_pdrb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>9111</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Kabupaten Manokwari Selatan</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>0.6418008658567829</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pmtb_q3-25_prov vs implisit_q-to-q_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>9111</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Kabupaten Manokwari Selatan</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>-0.3566883189662468</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pdrb_q3-25_prov vs implisit_y-on-y_pdrb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>9111</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Kabupaten Manokwari Selatan</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>-0.03428846653075418</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pklnprt_q3-25_prov vs implisit_y-on-y_pklnprt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>9111</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Kabupaten Manokwari Selatan</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>-4.27071025834069</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>sog_y-on-y_pi_q3-25</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>9112</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kabupaten Pegunungan Arfak</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>-4.066543314806655</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>sog_y-on-y_pi_q1-25_ril vs sog_y-on-y_pi_q1-25_rev</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>9112</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Pegunungan Arfak</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>10.9023210680644</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>sog_y-on-y_pi_q2-25_ril vs sog_y-on-y_pi_q2-25_rev</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>9112</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Pegunungan Arfak</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>-0.03836684496366132</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>q-to-q_pkrt_q3-25_prov vs q-to-q_pkrt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>9112</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Pegunungan Arfak</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>0.7486385182309321</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q3-25_prov vs q-to-q_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>9112</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Pegunungan Arfak</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>0.6017265497642872</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>q-to-q_pmtb_q3-25_prov vs q-to-q_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>9112</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Pegunungan Arfak</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>4.440128928794145</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>y-on-y_pdrb_q3-25_prov vs y-on-y_pdrb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>9112</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kabupaten Pegunungan Arfak</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>1.617458631167424</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>y-on-y_pkrt_q3-25_prov vs y-on-y_pkrt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>9112</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kabupaten Pegunungan Arfak</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>1.395395165062563</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>c-to-c_pkrt_q3-25_prov vs c-to-c_pkrt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9112</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kabupaten Pegunungan Arfak</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>0.6765440889855034</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>c-to-c_pmtb_q3-25_prov vs c-to-c_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>9112</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Kabupaten Pegunungan Arfak</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>-0.3379972166804031</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pdrb_q3-25_prov vs implisit_q-to-q_pdrb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>9112</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Kabupaten Pegunungan Arfak</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>-0.04940848767743523</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pmtb_q3-25_prov vs implisit_q-to-q_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>9112</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Kabupaten Pegunungan Arfak</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>-0.3428010617756844</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pdrb_q3-25_prov vs implisit_y-on-y_pdrb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>9112</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Kabupaten Pegunungan Arfak</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>0.2744972410446783</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pkp_q3-25_prov vs implisit_y-on-y_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
         </is>
       </c>
     </row>

--- a/data/output/evaluasi_91.xlsx
+++ b/data/output/evaluasi_91.xlsx
@@ -575,7 +575,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,3 point)</t>
+          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
         </is>
       </c>
     </row>
@@ -603,7 +603,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -631,7 +631,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -659,7 +659,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -687,7 +687,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -715,7 +715,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -771,7 +771,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -799,7 +799,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,05 point)</t>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
         </is>
       </c>
     </row>
@@ -855,7 +855,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -883,7 +883,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,05 point)</t>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
         </is>
       </c>
     </row>
@@ -911,7 +911,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -939,7 +939,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -995,7 +995,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -1023,7 +1023,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,05 point)</t>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
         </is>
       </c>
     </row>
@@ -1051,7 +1051,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -1079,7 +1079,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -1107,7 +1107,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -1135,7 +1135,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -1163,7 +1163,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -1191,7 +1191,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -1219,7 +1219,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -1247,7 +1247,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -1275,7 +1275,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -1555,7 +1555,7 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Diskrepansi Implisit Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi Implisit Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -1583,7 +1583,7 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Diskrepansi Implisit Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi Implisit Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -1611,7 +1611,7 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Diskrepansi Implisit Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi Implisit Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -1639,7 +1639,7 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Diskrepansi Implisit Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi Implisit Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -1667,7 +1667,7 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Diskrepansi Implisit Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi Implisit Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -1695,7 +1695,7 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Diskrepansi Implisit Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi Implisit Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -1723,7 +1723,7 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Diskrepansi Implisit Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi Implisit Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -1751,7 +1751,7 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Diskrepansi Implisit Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi Implisit Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -1779,7 +1779,7 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Diskrepansi Implisit Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi Implisit Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -1807,7 +1807,7 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Diskrepansi Implisit Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi Implisit Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
